--- a/NSO_regions_01.07.2025.xlsx
+++ b/NSO_regions_01.07.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92BA3A2-BB13-43BB-9ED2-BF6EBEB749DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635EF57B-4977-451B-8734-CB2727E4D92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -228,9 +228,6 @@
     <t>Уровень потребности в развитии дистанционного банковского обслуживания (Уровень потребности в ДБО)</t>
   </si>
   <si>
-    <t>Изменение уровня потребности в ДБО за счет создания альтернативной инфраструктуры, п.п.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Уровень потребности в ДБО с учетом созданной альтернативной инфраструктуры </t>
   </si>
   <si>
@@ -256,6 +253,9 @@
   </si>
   <si>
     <t>Уровень финансовой доступности</t>
+  </si>
+  <si>
+    <t>Изменение уровня потребности в ДБО за счет создания альтернативной инфраструктуры</t>
   </si>
 </sst>
 </file>
@@ -689,31 +689,31 @@
         <v>63</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>31</v>
